--- a/artfynd/A 63855-2025 artfynd.xlsx
+++ b/artfynd/A 63855-2025 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>131082787</v>
       </c>
       <c r="B3" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>131082785</v>
       </c>
       <c r="B4" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>131082788</v>
       </c>
       <c r="B6" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>131082786</v>
       </c>
       <c r="B7" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>131082774</v>
       </c>
       <c r="B9" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 63855-2025 artfynd.xlsx
+++ b/artfynd/A 63855-2025 artfynd.xlsx
@@ -1491,7 +1491,7 @@
         <v>131082774</v>
       </c>
       <c r="B9" t="n">
-        <v>91810</v>
+        <v>91813</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 63855-2025 artfynd.xlsx
+++ b/artfynd/A 63855-2025 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>131082787</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>131082785</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>131082788</v>
       </c>
       <c r="B6" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>131082786</v>
       </c>
       <c r="B7" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>131082774</v>
       </c>
       <c r="B9" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 63855-2025 artfynd.xlsx
+++ b/artfynd/A 63855-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131082777</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131082787</v>
       </c>
       <c r="B3" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>131082785</v>
       </c>
       <c r="B4" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>131082778</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>131082788</v>
       </c>
       <c r="B6" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>131082786</v>
       </c>
       <c r="B7" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>131082776</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>131082774</v>
       </c>
       <c r="B9" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,10 +1623,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131082775</v>
+        <v>131082779</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460143</v>
+        <v>459964</v>
       </c>
       <c r="R10" t="n">
-        <v>7046505</v>
+        <v>7046508</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, några meter upp på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant. Kring fyndplatsen finns en volym stående död ved av gran som indikerar högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1758,10 +1758,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131082779</v>
+        <v>131082775</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459964</v>
+        <v>460143</v>
       </c>
       <c r="R11" t="n">
-        <v>7046508</v>
+        <v>7046505</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant. Kring fyndplatsen finns en volym stående död ved av gran som indikerar högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack (savhack), färska och äldre, några meter upp på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 63855-2025 artfynd.xlsx
+++ b/artfynd/A 63855-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131082777</v>
       </c>
       <c r="B2" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131082787</v>
       </c>
       <c r="B3" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>131082785</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>131082778</v>
       </c>
       <c r="B5" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>131082788</v>
       </c>
       <c r="B6" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>131082786</v>
       </c>
       <c r="B7" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>131082776</v>
       </c>
       <c r="B8" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>131082774</v>
       </c>
       <c r="B9" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,10 +1623,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131082779</v>
+        <v>131082775</v>
       </c>
       <c r="B10" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459964</v>
+        <v>460143</v>
       </c>
       <c r="R10" t="n">
-        <v>7046508</v>
+        <v>7046505</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant. Kring fyndplatsen finns en volym stående död ved av gran som indikerar högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack (savhack), färska och äldre, några meter upp på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1758,10 +1758,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131082775</v>
+        <v>131082779</v>
       </c>
       <c r="B11" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460143</v>
+        <v>459964</v>
       </c>
       <c r="R11" t="n">
-        <v>7046505</v>
+        <v>7046508</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, några meter upp på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant. Kring fyndplatsen finns en volym stående död ved av gran som indikerar högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 63855-2025 artfynd.xlsx
+++ b/artfynd/A 63855-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131082777</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131082787</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>131082785</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>131082778</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>131082788</v>
       </c>
       <c r="B6" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>131082786</v>
       </c>
       <c r="B7" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>131082776</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>131082774</v>
       </c>
       <c r="B9" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,10 +1623,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131082775</v>
+        <v>131082779</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460143</v>
+        <v>459964</v>
       </c>
       <c r="R10" t="n">
-        <v>7046505</v>
+        <v>7046508</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, några meter upp på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant. Kring fyndplatsen finns en volym stående död ved av gran som indikerar högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1758,10 +1758,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131082779</v>
+        <v>131082775</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459964</v>
+        <v>460143</v>
       </c>
       <c r="R11" t="n">
-        <v>7046508</v>
+        <v>7046505</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant. Kring fyndplatsen finns en volym stående död ved av gran som indikerar högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack (savhack), färska och äldre, några meter upp på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 63855-2025 artfynd.xlsx
+++ b/artfynd/A 63855-2025 artfynd.xlsx
@@ -1623,7 +1623,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131082779</v>
+        <v>131082775</v>
       </c>
       <c r="B10" t="n">
         <v>57888</v>
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459964</v>
+        <v>460143</v>
       </c>
       <c r="R10" t="n">
-        <v>7046508</v>
+        <v>7046505</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant. Kring fyndplatsen finns en volym stående död ved av gran som indikerar högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack (savhack), färska och äldre, några meter upp på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1758,7 +1758,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131082775</v>
+        <v>131082779</v>
       </c>
       <c r="B11" t="n">
         <v>57888</v>
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460143</v>
+        <v>459964</v>
       </c>
       <c r="R11" t="n">
-        <v>7046505</v>
+        <v>7046508</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, några meter upp på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant. Kring fyndplatsen finns en volym stående död ved av gran som indikerar högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 63855-2025 artfynd.xlsx
+++ b/artfynd/A 63855-2025 artfynd.xlsx
@@ -1491,7 +1491,7 @@
         <v>131082774</v>
       </c>
       <c r="B9" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>131082775</v>
       </c>
       <c r="B10" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>131082779</v>
       </c>
       <c r="B11" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 63855-2025 artfynd.xlsx
+++ b/artfynd/A 63855-2025 artfynd.xlsx
@@ -1623,10 +1623,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131082775</v>
+        <v>131082779</v>
       </c>
       <c r="B10" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460143</v>
+        <v>459964</v>
       </c>
       <c r="R10" t="n">
-        <v>7046505</v>
+        <v>7046508</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, några meter upp på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant. Kring fyndplatsen finns en volym stående död ved av gran som indikerar högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1758,10 +1758,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131082779</v>
+        <v>131082775</v>
       </c>
       <c r="B11" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459964</v>
+        <v>460143</v>
       </c>
       <c r="R11" t="n">
-        <v>7046508</v>
+        <v>7046505</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant. Kring fyndplatsen finns en volym stående död ved av gran som indikerar högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack (savhack), färska och äldre, några meter upp på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 63855-2025 artfynd.xlsx
+++ b/artfynd/A 63855-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131082777</v>
+        <v>131082774</v>
       </c>
       <c r="B2" t="n">
-        <v>57888</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,29 +686,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460021</v>
+        <v>460010</v>
       </c>
       <c r="R2" t="n">
-        <v>7046535</v>
+        <v>7046547</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +757,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>I en upplyft granlåga.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,6 +766,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,12 +787,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,14 +810,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131082787</v>
+        <v>131082785</v>
       </c>
       <c r="B3" t="n">
-        <v>79250</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460089</v>
+        <v>460143</v>
       </c>
       <c r="R3" t="n">
-        <v>7046523</v>
+        <v>7046509</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +885,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På både gran och björk.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,14 +912,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131082785</v>
+        <v>131082786</v>
       </c>
       <c r="B4" t="n">
-        <v>79250</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460143</v>
+        <v>460119</v>
       </c>
       <c r="R4" t="n">
-        <v>7046509</v>
+        <v>7046519</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På både gran och björk.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,53 +1014,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131082778</v>
+        <v>131082787</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hävlarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459982</v>
+        <v>460089</v>
       </c>
       <c r="R5" t="n">
-        <v>7046511</v>
+        <v>7046523</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,7 +1089,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,31 +1100,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1152,11 +1119,11 @@
         <v>131082788</v>
       </c>
       <c r="B6" t="n">
-        <v>79250</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1251,14 +1218,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131082786</v>
+        <v>131082789</v>
       </c>
       <c r="B7" t="n">
-        <v>79250</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1286,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460119</v>
+        <v>459958</v>
       </c>
       <c r="R7" t="n">
-        <v>7046519</v>
+        <v>7046508</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1326,7 +1293,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>På en stående död gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,53 +1320,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131082776</v>
+        <v>131082790</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hävlarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460068</v>
+        <v>459913</v>
       </c>
       <c r="R8" t="n">
-        <v>7046530</v>
+        <v>7046493</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1395,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre på gränsen till färska, på en gran några meter in i granskogen från en hyggeskant.</t>
+          <t>På flera stående döda granar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,31 +1406,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1488,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131082774</v>
+        <v>131082775</v>
       </c>
       <c r="B9" t="n">
-        <v>91821</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,28 +1433,29 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1530,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460010</v>
+        <v>460143</v>
       </c>
       <c r="R9" t="n">
-        <v>7046547</v>
+        <v>7046505</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,7 +1505,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I en upplyft granlåga.</t>
+          <t>Ringhack (savhack), färska och äldre, några meter upp på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,7 +1514,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1600,12 +1534,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1623,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131082779</v>
+        <v>131082776</v>
       </c>
       <c r="B10" t="n">
-        <v>57892</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1590,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1666,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459964</v>
+        <v>460068</v>
       </c>
       <c r="R10" t="n">
-        <v>7046508</v>
+        <v>7046530</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,7 +1640,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant. Kring fyndplatsen finns en volym stående död ved av gran som indikerar högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack (savhack), äldre på gränsen till färska, på en gran några meter in i granskogen från en hyggeskant.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1758,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131082775</v>
+        <v>131082777</v>
       </c>
       <c r="B11" t="n">
-        <v>57892</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1791,7 +1725,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1801,10 +1735,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460143</v>
+        <v>460021</v>
       </c>
       <c r="R11" t="n">
-        <v>7046505</v>
+        <v>7046535</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1841,7 +1775,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, några meter upp på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1890,6 +1824,411 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131082778</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hävlarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>459982</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7046511</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131082779</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hävlarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>459964</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7046508</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på en gran vid en hyggeskant. Kring fyndplatsen finns en volym stående död ved av gran som indikerar högt livsmiljövärde för tretåig hackspett.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131082780</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hävlarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>459925</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7046501</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, i riklig mängd på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63855-2025 artfynd.xlsx
+++ b/artfynd/A 63855-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -807,6 +812,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131082774</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131082785</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131082786</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131082787</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131082788</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1317,6 +1347,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131082789</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1419,6 +1454,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131082790</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1554,6 +1594,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131082775</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1689,6 +1734,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131082776</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1824,6 +1874,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131082777</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1959,6 +2014,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131082778</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2094,6 +2154,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131082779</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2229,8 +2294,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131082780</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>